--- a/artfynd/A 26522-2026 artfynd.xlsx
+++ b/artfynd/A 26522-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127501166</v>
+        <v>127501163</v>
       </c>
       <c r="B2" t="n">
-        <v>110578</v>
+        <v>111405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680309</v>
+        <v>680305</v>
       </c>
       <c r="R2" t="n">
-        <v>6691935</v>
+        <v>6691991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,45 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127504231</v>
+        <v>127501164</v>
       </c>
       <c r="B3" t="n">
-        <v>105420</v>
+        <v>111405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>219719</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Snesslinge, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680305</v>
+        <v>680311</v>
       </c>
       <c r="R3" t="n">
-        <v>6691990</v>
+        <v>6691922</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -875,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Karolin Ring</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -886,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127501163</v>
+        <v>127501165</v>
       </c>
       <c r="B4" t="n">
-        <v>110578</v>
+        <v>111405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680305</v>
+        <v>680310</v>
       </c>
       <c r="R4" t="n">
-        <v>6691991</v>
+        <v>6691929</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127501169</v>
+        <v>127501166</v>
       </c>
       <c r="B5" t="n">
-        <v>103927</v>
+        <v>111405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,20 +1016,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>219719</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1031,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680305</v>
+        <v>680309</v>
       </c>
       <c r="R5" t="n">
-        <v>6691961</v>
+        <v>6691935</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,6 +1108,417 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127504231</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snesslinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>680305</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691990</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127501167</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snesslinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>680302</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691966</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127501168</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Snesslinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>680302</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691980</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127501169</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snesslinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>680305</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691961</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 26522-2026 artfynd.xlsx
+++ b/artfynd/A 26522-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501166</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127504231</t>
         </is>
       </c>
     </row>
@@ -1317,6 +1347,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501167</t>
         </is>
       </c>
     </row>
@@ -1421,6 +1456,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501168</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,8 +1563,23 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501169</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>